--- a/Result/profitability/1413.xlsx
+++ b/Result/profitability/1413.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04749999999999999</v>
+        <v>0.08124999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>3.51625</v>
+        <v>4.04</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01999999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="N3" t="n">
-        <v>3.135</v>
+        <v>3.6475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>-0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009999999999999995</v>
+        <v>0.05999999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>2.51625</v>
+        <v>3.0325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1020,10 +1020,10 @@
         <v>-0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08750000000000001</v>
+        <v>-0.1025</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.23625</v>
+        <v>-3.4925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.16375</v>
+        <v>-0.14</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.73375</v>
+        <v>-4.441249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1268,10 +1268,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.19125</v>
+        <v>-0.1575</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.72875</v>
+        <v>-4.11625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1395,10 +1395,10 @@
         <v>-0.49</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.25625</v>
+        <v>-0.2025</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.835</v>
+        <v>-4.798749999999999</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>569</v>
+      </c>
+      <c r="D75" t="n">
+        <v>527</v>
+      </c>
+      <c r="E75" t="n">
+        <v>42</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>48</v>
+      </c>
+      <c r="K75" t="n">
+        <v>40</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.08499999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.1825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.307692307692307</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-9.528735632183908</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2164730728616685</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
